--- a/artfynd/A 49329-2025 artfynd.xlsx
+++ b/artfynd/A 49329-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119075845</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112239463</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118879800</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141393</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88479705</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141356</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96539179</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,6 +1586,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141426</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1647,6 +1692,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88479704</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1755,6 +1805,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103857704</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1869,6 +1924,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96539174</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1981,6 +2041,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305788</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2082,6 +2147,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88479711</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2183,6 +2253,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88479696</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2291,6 +2366,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103857589</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2392,6 +2472,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88479702</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2508,6 +2593,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305568</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2616,6 +2706,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103857609</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2713,6 +2808,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88479714</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2810,6 +2910,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88479701</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2914,6 +3019,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103857573</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3014,8 +3124,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96539192</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 49329-2025 artfynd.xlsx
+++ b/artfynd/A 49329-2025 artfynd.xlsx
@@ -2816,10 +2816,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>88479701</v>
+        <v>96539192</v>
       </c>
       <c r="B21" t="n">
-        <v>89035</v>
+        <v>89206</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,21 +2827,33 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4398</v>
+        <v>4393</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitvaxing agg.</t>
+          <t>Papegojvaxing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>Gliophorus psittacinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Herink</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2880,12 +2892,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-10-10</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-10-10</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,13 +2924,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88479701</t>
+          <t>https://artportalen.se/Sighting/96539192</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103857573</v>
+        <v>88479701</v>
       </c>
       <c r="B22" t="n">
         <v>89035</v>
@@ -2943,20 +2955,22 @@
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Håvberget 3, Vansbro, Dlr</t>
+          <t>Håvberget SO, Håvberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479174</v>
+        <v>479162</v>
       </c>
       <c r="R22" t="n">
-        <v>6682205</v>
+        <v>6682218</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2980,22 +2994,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2020-10-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2020-10-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,6 +3008,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3021,16 +3026,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103857573</t>
+          <t>https://artportalen.se/Sighting/88479701</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96539192</v>
+        <v>103857573</v>
       </c>
       <c r="B23" t="n">
-        <v>89060</v>
+        <v>89035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,39 +3043,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>239221</v>
+        <v>4398</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vitvaxing agg.</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus var. psittacinus</t>
+          <t>Cuphophyllus virgineus s.lat.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Håvberget SO, Håvberget, Dlr</t>
+          <t>Håvberget 3, Vansbro, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479162</v>
+        <v>479174</v>
       </c>
       <c r="R23" t="n">
-        <v>6682218</v>
+        <v>6682205</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3094,12 +3094,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-10-08</t>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-10-08</t>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3108,7 +3118,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3126,7 +3135,7 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96539192</t>
+          <t>https://artportalen.se/Sighting/103857573</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 49329-2025 artfynd.xlsx
+++ b/artfynd/A 49329-2025 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>96539192</v>
       </c>
       <c r="B21" t="n">
-        <v>89206</v>
+        <v>89207</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
